--- a/2_ejecucion_plan_trabajo/2_consolidacion_datos_meteoro_epidemiologicos_reales/03_fusionados_y_limpieza_datos/df_final_fusionado_soi_sst.xlsx
+++ b/2_ejecucion_plan_trabajo/2_consolidacion_datos_meteoro_epidemiologicos_reales/03_fusionados_y_limpieza_datos/df_final_fusionado_soi_sst.xlsx
@@ -515,7 +515,7 @@
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>sst_anomaly</t>
+          <t>sst</t>
         </is>
       </c>
     </row>
